--- a/Analyses/mainStudy/01_dataPreperation/outputs/questionnaire/within_subjects/visual_trap_within.xlsx
+++ b/Analyses/mainStudy/01_dataPreperation/outputs/questionnaire/within_subjects/visual_trap_within.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,11 +398,11 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C2">
@@ -410,7 +410,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Planets</t>
+          <t>Circles</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -420,23 +420,23 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red Circle</t>
         </is>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1911</v>
+        <v>24676</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C3">
@@ -444,33 +444,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>CafeWall</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mostly on the bottom left of the square</t>
+          <t>Slanted / Diagonal</t>
         </is>
       </c>
       <c r="G3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1611</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C4">
@@ -478,7 +478,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Circles</t>
+          <t>Planets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -488,23 +488,23 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blue Circle</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="G4" t="b">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>848</v>
+        <v>91371</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C5">
@@ -512,33 +512,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lines</t>
+          <t>Collision</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Red Line</t>
+          <t>Green Triangle Only</t>
         </is>
       </c>
       <c r="G5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>883</v>
+        <v>53082</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C6">
@@ -546,33 +546,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CafeWall</t>
+          <t>Lines</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slanted / Diagonal</t>
+          <t>Blue Line</t>
         </is>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>810</v>
+        <v>13197</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C7">
@@ -580,7 +580,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Collision</t>
+          <t>Robot</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -590,23 +590,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blue Triangle and Orange Circle</t>
+          <t>Mostly around the center of the square</t>
         </is>
       </c>
       <c r="G7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>830</v>
+        <v>52883</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C8">
@@ -614,33 +614,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Collision</t>
+          <t>Planets</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Green Triangle Only</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>1643</v>
+        <v>66972</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C9">
@@ -653,28 +653,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Off-screen (outside the square)</t>
+          <t>Mostly around the center of the square</t>
         </is>
       </c>
       <c r="G9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>901</v>
+        <v>8187</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C10">
@@ -682,33 +682,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Planets</t>
+          <t>Circles</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red Circle</t>
         </is>
       </c>
       <c r="G10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>967</v>
+        <v>7672</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C11">
@@ -716,33 +716,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CafeWall</t>
+          <t>Lines</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Slightly curved</t>
+          <t>Blue Line</t>
         </is>
       </c>
       <c r="G11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>1300</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C12">
@@ -750,33 +750,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lines</t>
+          <t>CafeWall</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cannot be determined from the image</t>
+          <t>Slanted / Diagonal</t>
         </is>
       </c>
       <c r="G12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>891</v>
+        <v>46848</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C13">
@@ -784,24 +784,1248 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Collision</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Green Triangle Only</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>13703</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CafeWall</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Slanted / Diagonal</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>27768</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Robot</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mostly around the center of the square</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>26551</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Circles</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Cannot be determined from the image</t>
-        </is>
-      </c>
-      <c r="G13" t="b">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Red Circle</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>10623</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Collision</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Green Triangle Only</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>19504</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Planets</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>21567</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lines</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blue Line</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>6215</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>6</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C20">
         <v>0</v>
       </c>
-      <c r="H13">
-        <v>987</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Circles</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Red Circle</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>7196</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>6</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Planets</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>21229</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>6</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CafeWall</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Slanted / Diagonal</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>5495</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>6</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Robot</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mostly around the center of the square</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>11494</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Collision</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Green Triangle Only</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>104795</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Lines</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blue Line</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>3502</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>7</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lines</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blue Line</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>31763</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>7</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Robot</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mostly around the center of the square</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>36272</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>7</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Collision</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Green Triangle Only</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>25083</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>7</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Planets</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>34455</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>7</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CafeWall</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Slanted / Diagonal</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>43946</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>7</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Circles</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Red Circle</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>21105</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>8</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Planets</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>23585</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>8</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Collision</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Green Triangle Only</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>24823</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>8</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CafeWall</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Slanted / Diagonal</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>13989</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>8</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Robot</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mostly around the center of the square</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>22490</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>8</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Circles</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Red Circle</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>5701</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>8</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Lines</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blue Line</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>5962</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>9</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Robot</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mostly around the center of the square</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>30011</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>9</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Circles</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Red Circle</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>11597</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>9</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Collision</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Green Triangle Only</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>38732</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CafeWall</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Slanted / Diagonal</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>9227</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>9</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Planets</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>33222</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>9</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Lines</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blue Line</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>7322</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>11</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CafeWall</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Slanted / Diagonal</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>10239</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>11</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Robot</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mostly on the upper right of the square</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>13576</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>11</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Circles</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Red Circle</t>
+        </is>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>10390</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>11</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Collision</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Green Triangle Only</t>
+        </is>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>10777</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>11</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Planets</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>26044</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>11</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>5</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Lines</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blue Line</t>
+        </is>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>4017</v>
       </c>
     </row>
   </sheetData>
